--- a/02_Documentation/Airline_Cleaning_Audit.xlsx
+++ b/02_Documentation/Airline_Cleaning_Audit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Baseline Captured</t>
+          <t>Baseline captured</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -459,6 +459,162 @@
         </is>
       </c>
       <c r="B4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Column names standardized</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FlightDate converted to datetime</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Numeric data types standardized</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Categorical data types standardized</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cancellation logic validated</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Delay indicators validated</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Negative delays validated</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Diversion logic validated</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Time fields validated</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Range checks performed</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Duplicate check performed</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Final empty-column check performed</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Final data-type audit performed</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
